--- a/Du_lieu_mau_GDPT2018_30lop.xlsx
+++ b/Du_lieu_mau_GDPT2018_30lop.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0844B5-C3E4-47A3-A523-9AFB29DC3064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Huong_dan" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Nguon_tham_khao" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="DM_Mon_GDPT2018" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="DM_Giao_vien" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="DM_Lop" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="DM_To_hop" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Phan_cong" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="DM_Phong" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Tong_hop_GV" state="visible" r:id="rId12"/>
+    <sheet name="Huong_dan" sheetId="1" r:id="rId1"/>
+    <sheet name="Nguon_tham_khao" sheetId="2" r:id="rId2"/>
+    <sheet name="DM_Mon_GDPT2018" sheetId="3" r:id="rId3"/>
+    <sheet name="DM_Giao_vien" sheetId="4" r:id="rId4"/>
+    <sheet name="DM_Lop" sheetId="5" r:id="rId5"/>
+    <sheet name="DM_To_hop" sheetId="6" r:id="rId6"/>
+    <sheet name="Phan_cong" sheetId="7" r:id="rId7"/>
+    <sheet name="DM_Phong" sheetId="8" r:id="rId8"/>
+    <sheet name="Tong_hop_GV" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -1755,25 +1759,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="14"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1787,11 +1791,11 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1892,7 +1896,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1927,6 +1931,10 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2265,21 +2273,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" ht="26.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" s="12"/>
+    </row>
+    <row r="2" spans="1:2" ht="20.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2287,7 +2295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -2295,7 +2303,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2303,7 +2311,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
@@ -2311,7 +2319,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -2319,7 +2327,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
@@ -2327,7 +2335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>13</v>
       </c>
@@ -2335,7 +2343,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -2343,7 +2351,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>17</v>
       </c>
@@ -2351,7 +2359,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
@@ -2359,7 +2367,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
@@ -2367,7 +2375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>23</v>
       </c>
@@ -2380,26 +2388,26 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="105.140625" customWidth="1"/>
+    <col min="2" max="2" width="105.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" ht="26.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" s="12"/>
+    </row>
+    <row r="2" spans="1:2" ht="20.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
@@ -2407,7 +2415,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>27</v>
       </c>
@@ -2415,7 +2423,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>29</v>
       </c>
@@ -2423,7 +2431,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
@@ -2431,7 +2439,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>33</v>
       </c>
@@ -2439,7 +2447,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>35</v>
       </c>
@@ -2452,30 +2460,30 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" customWidth="1"/>
-    <col min="2" max="2" width="41.140625" customWidth="1"/>
-    <col min="3" max="3" width="25.140625" customWidth="1"/>
-    <col min="4" max="4" width="34.5703125" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="41.109375" customWidth="1"/>
+    <col min="3" max="3" width="25.109375" customWidth="1"/>
+    <col min="4" max="4" width="34.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1"/>
-      <c r="F1"/>
-    </row>
-    <row r="2" ht="26.1" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="12"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+    </row>
+    <row r="2" spans="1:6" ht="20.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>37</v>
       </c>
@@ -2489,7 +2497,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
@@ -2503,7 +2511,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>45</v>
       </c>
@@ -2517,7 +2525,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>47</v>
       </c>
@@ -2531,7 +2539,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>50</v>
       </c>
@@ -2545,7 +2553,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>53</v>
       </c>
@@ -2559,7 +2567,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>56</v>
       </c>
@@ -2573,7 +2581,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>58</v>
       </c>
@@ -2587,7 +2595,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>61</v>
       </c>
@@ -2601,7 +2609,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>63</v>
       </c>
@@ -2615,7 +2623,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>67</v>
       </c>
@@ -2629,7 +2637,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>69</v>
       </c>
@@ -2643,7 +2651,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>71</v>
       </c>
@@ -2657,7 +2665,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>73</v>
       </c>
@@ -2671,7 +2679,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>75</v>
       </c>
@@ -2685,7 +2693,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>78</v>
       </c>
@@ -2699,7 +2707,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>80</v>
       </c>
@@ -2713,7 +2721,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>83</v>
       </c>
@@ -2727,7 +2735,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>85</v>
       </c>
@@ -2741,7 +2749,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>89</v>
       </c>
@@ -2760,14 +2768,14 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K73"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -2781,7 +2789,7 @@
     <col min="11" max="11" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>92</v>
       </c>
@@ -2816,7 +2824,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>93</v>
       </c>
@@ -2851,7 +2859,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>103</v>
       </c>
@@ -2886,7 +2894,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>109</v>
       </c>
@@ -2921,7 +2929,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>113</v>
       </c>
@@ -2956,7 +2964,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>117</v>
       </c>
@@ -2991,7 +2999,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>121</v>
       </c>
@@ -3026,7 +3034,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>125</v>
       </c>
@@ -3061,7 +3069,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>129</v>
       </c>
@@ -3096,7 +3104,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>133</v>
       </c>
@@ -3131,7 +3139,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>137</v>
       </c>
@@ -3166,7 +3174,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>141</v>
       </c>
@@ -3201,7 +3209,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>146</v>
       </c>
@@ -3236,7 +3244,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>151</v>
       </c>
@@ -3271,7 +3279,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>155</v>
       </c>
@@ -3306,7 +3314,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>159</v>
       </c>
@@ -3341,7 +3349,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>163</v>
       </c>
@@ -3376,7 +3384,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>167</v>
       </c>
@@ -3411,7 +3419,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>171</v>
       </c>
@@ -3446,7 +3454,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>175</v>
       </c>
@@ -3481,7 +3489,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>180</v>
       </c>
@@ -3516,7 +3524,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>185</v>
       </c>
@@ -3551,7 +3559,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>189</v>
       </c>
@@ -3586,7 +3594,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>193</v>
       </c>
@@ -3621,7 +3629,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>197</v>
       </c>
@@ -3656,7 +3664,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>201</v>
       </c>
@@ -3691,7 +3699,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>205</v>
       </c>
@@ -3726,7 +3734,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>209</v>
       </c>
@@ -3761,7 +3769,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>214</v>
       </c>
@@ -3796,7 +3804,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>219</v>
       </c>
@@ -3831,7 +3839,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>223</v>
       </c>
@@ -3866,7 +3874,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>227</v>
       </c>
@@ -3901,7 +3909,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>231</v>
       </c>
@@ -3936,7 +3944,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>236</v>
       </c>
@@ -3971,7 +3979,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>241</v>
       </c>
@@ -4006,7 +4014,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>245</v>
       </c>
@@ -4041,7 +4049,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>249</v>
       </c>
@@ -4076,7 +4084,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>253</v>
       </c>
@@ -4111,7 +4119,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>258</v>
       </c>
@@ -4146,7 +4154,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>262</v>
       </c>
@@ -4181,7 +4189,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>266</v>
       </c>
@@ -4216,7 +4224,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>270</v>
       </c>
@@ -4251,7 +4259,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>274</v>
       </c>
@@ -4286,7 +4294,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>277</v>
       </c>
@@ -4321,7 +4329,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>281</v>
       </c>
@@ -4356,7 +4364,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>284</v>
       </c>
@@ -4391,7 +4399,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>287</v>
       </c>
@@ -4426,7 +4434,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>292</v>
       </c>
@@ -4461,7 +4469,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>296</v>
       </c>
@@ -4496,7 +4504,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>300</v>
       </c>
@@ -4531,7 +4539,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>304</v>
       </c>
@@ -4566,7 +4574,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>307</v>
       </c>
@@ -4601,7 +4609,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>311</v>
       </c>
@@ -4636,7 +4644,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>314</v>
       </c>
@@ -4671,7 +4679,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>317</v>
       </c>
@@ -4706,7 +4714,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>320</v>
       </c>
@@ -4741,7 +4749,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>324</v>
       </c>
@@ -4776,7 +4784,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>327</v>
       </c>
@@ -4811,7 +4819,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>330</v>
       </c>
@@ -4846,7 +4854,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>334</v>
       </c>
@@ -4881,7 +4889,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>338</v>
       </c>
@@ -4916,7 +4924,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>341</v>
       </c>
@@ -4951,7 +4959,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>344</v>
       </c>
@@ -4986,7 +4994,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>347</v>
       </c>
@@ -5021,7 +5029,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>350</v>
       </c>
@@ -5056,7 +5064,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>354</v>
       </c>
@@ -5091,7 +5099,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>357</v>
       </c>
@@ -5126,7 +5134,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>360</v>
       </c>
@@ -5161,7 +5169,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>364</v>
       </c>
@@ -5196,7 +5204,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>367</v>
       </c>
@@ -5231,7 +5239,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>370</v>
       </c>
@@ -5266,7 +5274,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>373</v>
       </c>
@@ -5301,7 +5309,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>376</v>
       </c>
@@ -5338,14 +5346,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -5357,7 +5365,7 @@
     <col min="9" max="9" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>379</v>
       </c>
@@ -5386,7 +5394,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>380</v>
       </c>
@@ -5415,7 +5423,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>105</v>
       </c>
@@ -5444,7 +5452,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>111</v>
       </c>
@@ -5473,7 +5481,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>115</v>
       </c>
@@ -5502,7 +5510,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>119</v>
       </c>
@@ -5531,7 +5539,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>123</v>
       </c>
@@ -5560,7 +5568,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>127</v>
       </c>
@@ -5589,7 +5597,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>131</v>
       </c>
@@ -5618,7 +5626,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>135</v>
       </c>
@@ -5647,7 +5655,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>139</v>
       </c>
@@ -5676,7 +5684,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>143</v>
       </c>
@@ -5705,7 +5713,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>173</v>
       </c>
@@ -5734,7 +5742,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>177</v>
       </c>
@@ -5763,7 +5771,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>148</v>
       </c>
@@ -5792,7 +5800,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>153</v>
       </c>
@@ -5821,7 +5829,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>191</v>
       </c>
@@ -5850,7 +5858,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>195</v>
       </c>
@@ -5879,7 +5887,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -5908,7 +5916,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>203</v>
       </c>
@@ -5937,7 +5945,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>207</v>
       </c>
@@ -5966,7 +5974,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>216</v>
       </c>
@@ -5995,7 +6003,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>225</v>
       </c>
@@ -6024,7 +6032,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>233</v>
       </c>
@@ -6053,7 +6061,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>221</v>
       </c>
@@ -6082,7 +6090,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>279</v>
       </c>
@@ -6111,7 +6119,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>238</v>
       </c>
@@ -6140,7 +6148,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>247</v>
       </c>
@@ -6169,7 +6177,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>298</v>
       </c>
@@ -6198,7 +6206,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>294</v>
       </c>
@@ -6227,7 +6235,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>289</v>
       </c>
@@ -6256,7 +6264,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>255</v>
       </c>
@@ -6287,14 +6295,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -6304,7 +6312,7 @@
     <col min="10" max="10" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>447</v>
       </c>
@@ -6327,7 +6335,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>384</v>
       </c>
@@ -6350,7 +6358,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>389</v>
       </c>
@@ -6373,7 +6381,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>398</v>
       </c>
@@ -6396,7 +6404,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>403</v>
       </c>
@@ -6419,7 +6427,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>406</v>
       </c>
@@ -6442,7 +6450,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>411</v>
       </c>
@@ -6465,7 +6473,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>444</v>
       </c>
@@ -6488,7 +6496,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>389</v>
       </c>
@@ -6511,7 +6519,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>398</v>
       </c>
@@ -6534,7 +6542,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>403</v>
       </c>
@@ -6557,7 +6565,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>406</v>
       </c>
@@ -6580,7 +6588,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>411</v>
       </c>
@@ -6603,7 +6611,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>444</v>
       </c>
@@ -6626,7 +6634,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>389</v>
       </c>
@@ -6649,7 +6657,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>398</v>
       </c>
@@ -6672,7 +6680,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>403</v>
       </c>
@@ -6695,7 +6703,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>406</v>
       </c>
@@ -6718,7 +6726,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>411</v>
       </c>
@@ -6741,7 +6749,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>444</v>
       </c>
@@ -6766,14 +6774,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:O508"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -6788,10 +6796,10 @@
     <col min="12" max="12" width="26" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="26" customWidth="1"/>
-    <col min="15" max="15" width="30" customWidth="1"/>
+    <col min="15" max="15" width="36.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>455</v>
       </c>
@@ -6838,7 +6846,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>456</v>
       </c>
@@ -6885,7 +6893,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -6932,7 +6940,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -6979,7 +6987,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -7026,7 +7034,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -7073,7 +7081,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -7120,7 +7128,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -7167,7 +7175,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -7214,7 +7222,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -7261,7 +7269,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -7308,7 +7316,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>10</v>
       </c>
@@ -7355,7 +7363,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -7402,7 +7410,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>12</v>
       </c>
@@ -7449,7 +7457,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -7496,7 +7504,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>14</v>
       </c>
@@ -7543,7 +7551,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -7590,7 +7598,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>16</v>
       </c>
@@ -7637,7 +7645,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -7684,7 +7692,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>18</v>
       </c>
@@ -7731,7 +7739,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -7778,7 +7786,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>20</v>
       </c>
@@ -7825,7 +7833,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -7872,7 +7880,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>22</v>
       </c>
@@ -7919,7 +7927,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -7966,7 +7974,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>24</v>
       </c>
@@ -8013,7 +8021,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>25</v>
       </c>
@@ -8060,7 +8068,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>26</v>
       </c>
@@ -8107,7 +8115,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>27</v>
       </c>
@@ -8154,7 +8162,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>28</v>
       </c>
@@ -8201,7 +8209,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>29</v>
       </c>
@@ -8248,7 +8256,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>30</v>
       </c>
@@ -8295,7 +8303,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>31</v>
       </c>
@@ -8342,7 +8350,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>32</v>
       </c>
@@ -8389,7 +8397,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>33</v>
       </c>
@@ -8436,7 +8444,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>34</v>
       </c>
@@ -8483,7 +8491,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>35</v>
       </c>
@@ -8530,7 +8538,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>36</v>
       </c>
@@ -8577,7 +8585,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>37</v>
       </c>
@@ -8624,7 +8632,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>38</v>
       </c>
@@ -8671,7 +8679,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>39</v>
       </c>
@@ -8718,7 +8726,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>40</v>
       </c>
@@ -8765,7 +8773,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>41</v>
       </c>
@@ -8812,7 +8820,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>42</v>
       </c>
@@ -8859,7 +8867,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>43</v>
       </c>
@@ -8906,7 +8914,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>44</v>
       </c>
@@ -8953,7 +8961,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>45</v>
       </c>
@@ -9000,7 +9008,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>46</v>
       </c>
@@ -9047,7 +9055,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>47</v>
       </c>
@@ -9094,7 +9102,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>48</v>
       </c>
@@ -9141,7 +9149,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>49</v>
       </c>
@@ -9188,7 +9196,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>50</v>
       </c>
@@ -9235,7 +9243,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>51</v>
       </c>
@@ -9282,7 +9290,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>52</v>
       </c>
@@ -9329,7 +9337,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>53</v>
       </c>
@@ -9376,7 +9384,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>54</v>
       </c>
@@ -9423,7 +9431,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>55</v>
       </c>
@@ -9470,7 +9478,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>56</v>
       </c>
@@ -9517,7 +9525,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>57</v>
       </c>
@@ -9564,7 +9572,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>58</v>
       </c>
@@ -9611,7 +9619,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>59</v>
       </c>
@@ -9658,7 +9666,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>60</v>
       </c>
@@ -9705,7 +9713,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>61</v>
       </c>
@@ -9752,7 +9760,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>62</v>
       </c>
@@ -9799,7 +9807,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>63</v>
       </c>
@@ -9846,7 +9854,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>64</v>
       </c>
@@ -9893,7 +9901,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>65</v>
       </c>
@@ -9940,7 +9948,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>66</v>
       </c>
@@ -9987,7 +9995,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>67</v>
       </c>
@@ -10034,7 +10042,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>68</v>
       </c>
@@ -10081,7 +10089,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>69</v>
       </c>
@@ -10128,7 +10136,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>70</v>
       </c>
@@ -10175,7 +10183,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>71</v>
       </c>
@@ -10222,7 +10230,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>72</v>
       </c>
@@ -10269,7 +10277,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>73</v>
       </c>
@@ -10316,7 +10324,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>74</v>
       </c>
@@ -10363,7 +10371,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>75</v>
       </c>
@@ -10410,7 +10418,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>76</v>
       </c>
@@ -10457,7 +10465,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>77</v>
       </c>
@@ -10504,7 +10512,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>78</v>
       </c>
@@ -10551,7 +10559,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>79</v>
       </c>
@@ -10598,7 +10606,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>80</v>
       </c>
@@ -10645,7 +10653,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>81</v>
       </c>
@@ -10692,7 +10700,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>82</v>
       </c>
@@ -10739,7 +10747,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>83</v>
       </c>
@@ -10786,7 +10794,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>84</v>
       </c>
@@ -10833,7 +10841,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>85</v>
       </c>
@@ -10880,7 +10888,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>86</v>
       </c>
@@ -10927,7 +10935,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>87</v>
       </c>
@@ -10974,7 +10982,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>88</v>
       </c>
@@ -11021,7 +11029,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>89</v>
       </c>
@@ -11068,7 +11076,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>90</v>
       </c>
@@ -11115,7 +11123,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>91</v>
       </c>
@@ -11162,7 +11170,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>92</v>
       </c>
@@ -11209,7 +11217,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>93</v>
       </c>
@@ -11256,7 +11264,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>94</v>
       </c>
@@ -11303,7 +11311,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>95</v>
       </c>
@@ -11350,7 +11358,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>96</v>
       </c>
@@ -11397,7 +11405,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>97</v>
       </c>
@@ -11444,7 +11452,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>98</v>
       </c>
@@ -11491,7 +11499,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>99</v>
       </c>
@@ -11538,7 +11546,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>100</v>
       </c>
@@ -11585,7 +11593,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>101</v>
       </c>
@@ -11632,7 +11640,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
         <v>102</v>
       </c>
@@ -11679,7 +11687,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>103</v>
       </c>
@@ -11726,7 +11734,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>104</v>
       </c>
@@ -11773,7 +11781,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>105</v>
       </c>
@@ -11820,7 +11828,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>106</v>
       </c>
@@ -11867,7 +11875,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>107</v>
       </c>
@@ -11914,7 +11922,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>108</v>
       </c>
@@ -11961,7 +11969,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>109</v>
       </c>
@@ -12008,7 +12016,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>110</v>
       </c>
@@ -12055,7 +12063,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>111</v>
       </c>
@@ -12102,7 +12110,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>112</v>
       </c>
@@ -12149,7 +12157,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>113</v>
       </c>
@@ -12196,7 +12204,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>114</v>
       </c>
@@ -12243,7 +12251,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>115</v>
       </c>
@@ -12290,7 +12298,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>116</v>
       </c>
@@ -12337,7 +12345,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>117</v>
       </c>
@@ -12384,7 +12392,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>118</v>
       </c>
@@ -12431,7 +12439,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>119</v>
       </c>
@@ -12478,7 +12486,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>120</v>
       </c>
@@ -12525,7 +12533,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>121</v>
       </c>
@@ -12572,7 +12580,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
         <v>122</v>
       </c>
@@ -12619,7 +12627,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>123</v>
       </c>
@@ -12666,7 +12674,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>124</v>
       </c>
@@ -12713,7 +12721,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>125</v>
       </c>
@@ -12760,7 +12768,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>126</v>
       </c>
@@ -12807,7 +12815,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>127</v>
       </c>
@@ -12854,7 +12862,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>128</v>
       </c>
@@ -12901,7 +12909,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>129</v>
       </c>
@@ -12948,7 +12956,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
         <v>130</v>
       </c>
@@ -12995,7 +13003,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>131</v>
       </c>
@@ -13042,7 +13050,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>132</v>
       </c>
@@ -13089,7 +13097,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>133</v>
       </c>
@@ -13136,7 +13144,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
         <v>134</v>
       </c>
@@ -13183,7 +13191,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>135</v>
       </c>
@@ -13230,7 +13238,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>136</v>
       </c>
@@ -13277,7 +13285,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>137</v>
       </c>
@@ -13324,7 +13332,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>138</v>
       </c>
@@ -13371,7 +13379,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>139</v>
       </c>
@@ -13418,7 +13426,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>140</v>
       </c>
@@ -13465,7 +13473,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>141</v>
       </c>
@@ -13512,7 +13520,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>142</v>
       </c>
@@ -13559,7 +13567,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>143</v>
       </c>
@@ -13606,7 +13614,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
         <v>144</v>
       </c>
@@ -13653,7 +13661,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
         <v>145</v>
       </c>
@@ -13700,7 +13708,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>146</v>
       </c>
@@ -13747,7 +13755,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
         <v>147</v>
       </c>
@@ -13794,7 +13802,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>148</v>
       </c>
@@ -13841,7 +13849,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
         <v>149</v>
       </c>
@@ -13888,7 +13896,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>150</v>
       </c>
@@ -13935,7 +13943,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
         <v>151</v>
       </c>
@@ -13982,7 +13990,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
         <v>152</v>
       </c>
@@ -14029,7 +14037,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
         <v>153</v>
       </c>
@@ -14076,7 +14084,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>154</v>
       </c>
@@ -14123,7 +14131,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>155</v>
       </c>
@@ -14170,7 +14178,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
         <v>156</v>
       </c>
@@ -14217,7 +14225,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
         <v>157</v>
       </c>
@@ -14264,7 +14272,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
         <v>158</v>
       </c>
@@ -14311,7 +14319,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
         <v>159</v>
       </c>
@@ -14358,7 +14366,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
         <v>160</v>
       </c>
@@ -14405,7 +14413,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
         <v>161</v>
       </c>
@@ -14452,7 +14460,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
         <v>162</v>
       </c>
@@ -14499,7 +14507,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
         <v>163</v>
       </c>
@@ -14546,7 +14554,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
         <v>164</v>
       </c>
@@ -14593,7 +14601,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" s="3">
         <v>165</v>
       </c>
@@ -14640,7 +14648,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
         <v>166</v>
       </c>
@@ -14687,7 +14695,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
         <v>167</v>
       </c>
@@ -14734,7 +14742,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
         <v>168</v>
       </c>
@@ -14781,7 +14789,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>169</v>
       </c>
@@ -14828,7 +14836,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
         <v>170</v>
       </c>
@@ -14875,7 +14883,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>171</v>
       </c>
@@ -14922,7 +14930,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>172</v>
       </c>
@@ -14969,7 +14977,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>173</v>
       </c>
@@ -15016,7 +15024,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>174</v>
       </c>
@@ -15063,7 +15071,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>175</v>
       </c>
@@ -15110,7 +15118,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>176</v>
       </c>
@@ -15157,7 +15165,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>177</v>
       </c>
@@ -15204,7 +15212,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>178</v>
       </c>
@@ -15251,7 +15259,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
         <v>179</v>
       </c>
@@ -15298,7 +15306,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
         <v>180</v>
       </c>
@@ -15345,7 +15353,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>181</v>
       </c>
@@ -15392,7 +15400,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
         <v>182</v>
       </c>
@@ -15439,7 +15447,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>183</v>
       </c>
@@ -15486,7 +15494,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>184</v>
       </c>
@@ -15533,7 +15541,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>185</v>
       </c>
@@ -15580,7 +15588,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>186</v>
       </c>
@@ -15627,7 +15635,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
         <v>187</v>
       </c>
@@ -15674,7 +15682,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>188</v>
       </c>
@@ -15721,7 +15729,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>189</v>
       </c>
@@ -15768,7 +15776,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>190</v>
       </c>
@@ -15815,7 +15823,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
         <v>191</v>
       </c>
@@ -15862,7 +15870,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>192</v>
       </c>
@@ -15909,7 +15917,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>193</v>
       </c>
@@ -15956,7 +15964,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>194</v>
       </c>
@@ -16003,7 +16011,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>195</v>
       </c>
@@ -16050,7 +16058,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>196</v>
       </c>
@@ -16097,7 +16105,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>197</v>
       </c>
@@ -16144,7 +16152,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>198</v>
       </c>
@@ -16191,7 +16199,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>199</v>
       </c>
@@ -16238,7 +16246,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>200</v>
       </c>
@@ -16285,7 +16293,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
         <v>201</v>
       </c>
@@ -16332,7 +16340,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
         <v>202</v>
       </c>
@@ -16379,7 +16387,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A205" s="4">
         <v>203</v>
       </c>
@@ -16426,7 +16434,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
         <v>204</v>
       </c>
@@ -16473,7 +16481,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A207" s="4">
         <v>205</v>
       </c>
@@ -16520,7 +16528,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A208" s="3">
         <v>206</v>
       </c>
@@ -16567,7 +16575,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A209" s="4">
         <v>207</v>
       </c>
@@ -16614,7 +16622,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A210" s="3">
         <v>208</v>
       </c>
@@ -16661,7 +16669,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A211" s="4">
         <v>209</v>
       </c>
@@ -16708,7 +16716,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A212" s="3">
         <v>210</v>
       </c>
@@ -16755,7 +16763,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
         <v>211</v>
       </c>
@@ -16802,7 +16810,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A214" s="3">
         <v>212</v>
       </c>
@@ -16849,7 +16857,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A215" s="4">
         <v>213</v>
       </c>
@@ -16896,7 +16904,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A216" s="3">
         <v>214</v>
       </c>
@@ -16943,7 +16951,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A217" s="4">
         <v>215</v>
       </c>
@@ -16990,7 +16998,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A218" s="3">
         <v>216</v>
       </c>
@@ -17037,7 +17045,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A219" s="4">
         <v>217</v>
       </c>
@@ -17084,7 +17092,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A220" s="3">
         <v>218</v>
       </c>
@@ -17131,7 +17139,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A221" s="4">
         <v>219</v>
       </c>
@@ -17178,7 +17186,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A222" s="3">
         <v>220</v>
       </c>
@@ -17225,7 +17233,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
         <v>221</v>
       </c>
@@ -17272,7 +17280,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A224" s="3">
         <v>222</v>
       </c>
@@ -17319,7 +17327,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A225" s="4">
         <v>223</v>
       </c>
@@ -17366,7 +17374,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
         <v>224</v>
       </c>
@@ -17413,7 +17421,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A227" s="4">
         <v>225</v>
       </c>
@@ -17460,7 +17468,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
         <v>226</v>
       </c>
@@ -17507,7 +17515,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A229" s="4">
         <v>227</v>
       </c>
@@ -17554,7 +17562,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A230" s="3">
         <v>228</v>
       </c>
@@ -17601,7 +17609,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A231" s="4">
         <v>229</v>
       </c>
@@ -17648,7 +17656,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>230</v>
       </c>
@@ -17695,7 +17703,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A233" s="4">
         <v>231</v>
       </c>
@@ -17742,7 +17750,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>232</v>
       </c>
@@ -17789,7 +17797,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A235" s="4">
         <v>233</v>
       </c>
@@ -17836,7 +17844,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>234</v>
       </c>
@@ -17883,7 +17891,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
         <v>235</v>
       </c>
@@ -17930,7 +17938,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A238" s="3">
         <v>236</v>
       </c>
@@ -17977,7 +17985,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A239" s="4">
         <v>237</v>
       </c>
@@ -18024,7 +18032,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A240" s="3">
         <v>238</v>
       </c>
@@ -18071,7 +18079,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A241" s="4">
         <v>239</v>
       </c>
@@ -18118,7 +18126,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A242" s="3">
         <v>240</v>
       </c>
@@ -18165,7 +18173,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
         <v>241</v>
       </c>
@@ -18212,7 +18220,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A244" s="3">
         <v>242</v>
       </c>
@@ -18259,7 +18267,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A245" s="4">
         <v>243</v>
       </c>
@@ -18306,7 +18314,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A246" s="3">
         <v>244</v>
       </c>
@@ -18353,7 +18361,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A247" s="4">
         <v>245</v>
       </c>
@@ -18400,7 +18408,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A248" s="3">
         <v>246</v>
       </c>
@@ -18447,7 +18455,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
         <v>247</v>
       </c>
@@ -18494,7 +18502,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A250" s="3">
         <v>248</v>
       </c>
@@ -18541,7 +18549,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A251" s="4">
         <v>249</v>
       </c>
@@ -18588,7 +18596,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A252" s="3">
         <v>250</v>
       </c>
@@ -18635,7 +18643,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A253" s="4">
         <v>251</v>
       </c>
@@ -18682,7 +18690,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A254" s="3">
         <v>252</v>
       </c>
@@ -18729,7 +18737,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A255" s="4">
         <v>253</v>
       </c>
@@ -18776,7 +18784,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A256" s="3">
         <v>254</v>
       </c>
@@ -18823,7 +18831,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A257" s="4">
         <v>255</v>
       </c>
@@ -18870,7 +18878,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A258" s="3">
         <v>256</v>
       </c>
@@ -18917,7 +18925,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A259" s="4">
         <v>257</v>
       </c>
@@ -18964,7 +18972,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A260" s="3">
         <v>258</v>
       </c>
@@ -19011,7 +19019,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
         <v>259</v>
       </c>
@@ -19058,7 +19066,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A262" s="3">
         <v>260</v>
       </c>
@@ -19105,7 +19113,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A263" s="4">
         <v>261</v>
       </c>
@@ -19152,7 +19160,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A264" s="3">
         <v>262</v>
       </c>
@@ -19199,7 +19207,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A265" s="4">
         <v>263</v>
       </c>
@@ -19246,7 +19254,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A266" s="3">
         <v>264</v>
       </c>
@@ -19293,7 +19301,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A267" s="4">
         <v>265</v>
       </c>
@@ -19340,7 +19348,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A268" s="3">
         <v>266</v>
       </c>
@@ -19387,7 +19395,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A269" s="4">
         <v>267</v>
       </c>
@@ -19434,7 +19442,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A270" s="3">
         <v>268</v>
       </c>
@@ -19481,7 +19489,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A271" s="4">
         <v>269</v>
       </c>
@@ -19528,7 +19536,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A272" s="3">
         <v>270</v>
       </c>
@@ -19575,7 +19583,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A273" s="4">
         <v>271</v>
       </c>
@@ -19622,7 +19630,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A274" s="3">
         <v>272</v>
       </c>
@@ -19669,7 +19677,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A275" s="4">
         <v>273</v>
       </c>
@@ -19716,7 +19724,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A276" s="3">
         <v>274</v>
       </c>
@@ -19763,7 +19771,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A277" s="4">
         <v>275</v>
       </c>
@@ -19810,7 +19818,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A278" s="3">
         <v>276</v>
       </c>
@@ -19857,7 +19865,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A279" s="4">
         <v>277</v>
       </c>
@@ -19904,7 +19912,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A280" s="3">
         <v>278</v>
       </c>
@@ -19951,7 +19959,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A281" s="4">
         <v>279</v>
       </c>
@@ -19998,7 +20006,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A282" s="3">
         <v>280</v>
       </c>
@@ -20045,7 +20053,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A283" s="4">
         <v>281</v>
       </c>
@@ -20092,7 +20100,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A284" s="3">
         <v>282</v>
       </c>
@@ -20139,7 +20147,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A285" s="4">
         <v>283</v>
       </c>
@@ -20186,7 +20194,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A286" s="3">
         <v>284</v>
       </c>
@@ -20233,7 +20241,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A287" s="4">
         <v>285</v>
       </c>
@@ -20280,7 +20288,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A288" s="3">
         <v>286</v>
       </c>
@@ -20327,7 +20335,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A289" s="4">
         <v>287</v>
       </c>
@@ -20374,7 +20382,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A290" s="3">
         <v>288</v>
       </c>
@@ -20421,7 +20429,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A291" s="4">
         <v>289</v>
       </c>
@@ -20468,7 +20476,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A292" s="3">
         <v>290</v>
       </c>
@@ -20515,7 +20523,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A293" s="4">
         <v>291</v>
       </c>
@@ -20562,7 +20570,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A294" s="3">
         <v>292</v>
       </c>
@@ -20609,7 +20617,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A295" s="4">
         <v>293</v>
       </c>
@@ -20656,7 +20664,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A296" s="3">
         <v>294</v>
       </c>
@@ -20703,7 +20711,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A297" s="4">
         <v>295</v>
       </c>
@@ -20750,7 +20758,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A298" s="3">
         <v>296</v>
       </c>
@@ -20797,7 +20805,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A299" s="4">
         <v>297</v>
       </c>
@@ -20844,7 +20852,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A300" s="3">
         <v>298</v>
       </c>
@@ -20891,7 +20899,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A301" s="4">
         <v>299</v>
       </c>
@@ -20938,7 +20946,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A302" s="3">
         <v>300</v>
       </c>
@@ -20985,7 +20993,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A303" s="4">
         <v>301</v>
       </c>
@@ -21032,7 +21040,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A304" s="3">
         <v>302</v>
       </c>
@@ -21079,7 +21087,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A305" s="4">
         <v>303</v>
       </c>
@@ -21126,7 +21134,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A306" s="3">
         <v>304</v>
       </c>
@@ -21173,7 +21181,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A307" s="4">
         <v>305</v>
       </c>
@@ -21220,7 +21228,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A308" s="3">
         <v>306</v>
       </c>
@@ -21267,7 +21275,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A309" s="4">
         <v>307</v>
       </c>
@@ -21314,7 +21322,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A310" s="3">
         <v>308</v>
       </c>
@@ -21361,7 +21369,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A311" s="4">
         <v>309</v>
       </c>
@@ -21408,7 +21416,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A312" s="3">
         <v>310</v>
       </c>
@@ -21455,7 +21463,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A313" s="4">
         <v>311</v>
       </c>
@@ -21502,7 +21510,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A314" s="3">
         <v>312</v>
       </c>
@@ -21549,7 +21557,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A315" s="4">
         <v>313</v>
       </c>
@@ -21596,7 +21604,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A316" s="3">
         <v>314</v>
       </c>
@@ -21643,7 +21651,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A317" s="4">
         <v>315</v>
       </c>
@@ -21690,7 +21698,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A318" s="3">
         <v>316</v>
       </c>
@@ -21737,7 +21745,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A319" s="4">
         <v>317</v>
       </c>
@@ -21784,7 +21792,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A320" s="3">
         <v>318</v>
       </c>
@@ -21831,7 +21839,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A321" s="4">
         <v>319</v>
       </c>
@@ -21878,7 +21886,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A322" s="3">
         <v>320</v>
       </c>
@@ -21925,7 +21933,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A323" s="4">
         <v>321</v>
       </c>
@@ -21972,7 +21980,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A324" s="3">
         <v>322</v>
       </c>
@@ -22019,7 +22027,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A325" s="4">
         <v>323</v>
       </c>
@@ -22066,7 +22074,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A326" s="3">
         <v>324</v>
       </c>
@@ -22113,7 +22121,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A327" s="4">
         <v>325</v>
       </c>
@@ -22160,7 +22168,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A328" s="3">
         <v>326</v>
       </c>
@@ -22207,7 +22215,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A329" s="4">
         <v>327</v>
       </c>
@@ -22254,7 +22262,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A330" s="3">
         <v>328</v>
       </c>
@@ -22301,7 +22309,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A331" s="4">
         <v>329</v>
       </c>
@@ -22348,7 +22356,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A332" s="3">
         <v>330</v>
       </c>
@@ -22395,7 +22403,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A333" s="4">
         <v>331</v>
       </c>
@@ -22442,7 +22450,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A334" s="3">
         <v>332</v>
       </c>
@@ -22489,7 +22497,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A335" s="4">
         <v>333</v>
       </c>
@@ -22536,7 +22544,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A336" s="3">
         <v>334</v>
       </c>
@@ -22583,7 +22591,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A337" s="4">
         <v>335</v>
       </c>
@@ -22630,7 +22638,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A338" s="3">
         <v>336</v>
       </c>
@@ -22677,7 +22685,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A339" s="4">
         <v>337</v>
       </c>
@@ -22724,7 +22732,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A340" s="3">
         <v>338</v>
       </c>
@@ -22771,7 +22779,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A341" s="4">
         <v>339</v>
       </c>
@@ -22818,7 +22826,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A342" s="3">
         <v>340</v>
       </c>
@@ -22865,7 +22873,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A343" s="4">
         <v>341</v>
       </c>
@@ -22912,7 +22920,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A344" s="3">
         <v>342</v>
       </c>
@@ -22959,7 +22967,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A345" s="4">
         <v>343</v>
       </c>
@@ -23006,7 +23014,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A346" s="3">
         <v>344</v>
       </c>
@@ -23053,7 +23061,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A347" s="4">
         <v>345</v>
       </c>
@@ -23100,7 +23108,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A348" s="3">
         <v>346</v>
       </c>
@@ -23147,7 +23155,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A349" s="4">
         <v>347</v>
       </c>
@@ -23194,7 +23202,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A350" s="3">
         <v>348</v>
       </c>
@@ -23241,7 +23249,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A351" s="4">
         <v>349</v>
       </c>
@@ -23288,7 +23296,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A352" s="3">
         <v>350</v>
       </c>
@@ -23335,7 +23343,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A353" s="4">
         <v>351</v>
       </c>
@@ -23382,7 +23390,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A354" s="3">
         <v>352</v>
       </c>
@@ -23429,7 +23437,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A355" s="4">
         <v>353</v>
       </c>
@@ -23476,7 +23484,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A356" s="3">
         <v>354</v>
       </c>
@@ -23523,7 +23531,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A357" s="4">
         <v>355</v>
       </c>
@@ -23570,7 +23578,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A358" s="3">
         <v>356</v>
       </c>
@@ -23617,7 +23625,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A359" s="4">
         <v>357</v>
       </c>
@@ -23664,7 +23672,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A360" s="3">
         <v>358</v>
       </c>
@@ -23711,7 +23719,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A361" s="4">
         <v>359</v>
       </c>
@@ -23758,7 +23766,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A362" s="3">
         <v>360</v>
       </c>
@@ -23805,7 +23813,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A363" s="4">
         <v>361</v>
       </c>
@@ -23852,7 +23860,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A364" s="3">
         <v>362</v>
       </c>
@@ -23899,7 +23907,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A365" s="4">
         <v>363</v>
       </c>
@@ -23946,7 +23954,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A366" s="3">
         <v>364</v>
       </c>
@@ -23993,7 +24001,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A367" s="4">
         <v>365</v>
       </c>
@@ -24040,7 +24048,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A368" s="3">
         <v>366</v>
       </c>
@@ -24087,7 +24095,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A369" s="4">
         <v>367</v>
       </c>
@@ -24134,7 +24142,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="370" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A370" s="3">
         <v>368</v>
       </c>
@@ -24181,7 +24189,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A371" s="4">
         <v>369</v>
       </c>
@@ -24228,7 +24236,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="372" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A372" s="3">
         <v>370</v>
       </c>
@@ -24275,7 +24283,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A373" s="4">
         <v>371</v>
       </c>
@@ -24322,7 +24330,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A374" s="3">
         <v>372</v>
       </c>
@@ -24369,7 +24377,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A375" s="4">
         <v>373</v>
       </c>
@@ -24416,7 +24424,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A376" s="3">
         <v>374</v>
       </c>
@@ -24463,7 +24471,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A377" s="4">
         <v>375</v>
       </c>
@@ -24510,7 +24518,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A378" s="3">
         <v>376</v>
       </c>
@@ -24557,7 +24565,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A379" s="4">
         <v>377</v>
       </c>
@@ -24604,7 +24612,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="380" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A380" s="3">
         <v>378</v>
       </c>
@@ -24651,7 +24659,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A381" s="4">
         <v>379</v>
       </c>
@@ -24698,7 +24706,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="382" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A382" s="3">
         <v>380</v>
       </c>
@@ -24745,7 +24753,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A383" s="4">
         <v>381</v>
       </c>
@@ -24792,7 +24800,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="384" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A384" s="3">
         <v>382</v>
       </c>
@@ -24839,7 +24847,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A385" s="4">
         <v>383</v>
       </c>
@@ -24886,7 +24894,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A386" s="3">
         <v>384</v>
       </c>
@@ -24933,7 +24941,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A387" s="4">
         <v>385</v>
       </c>
@@ -24980,7 +24988,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A388" s="3">
         <v>386</v>
       </c>
@@ -25027,7 +25035,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A389" s="4">
         <v>387</v>
       </c>
@@ -25074,7 +25082,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A390" s="3">
         <v>388</v>
       </c>
@@ -25121,7 +25129,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A391" s="4">
         <v>389</v>
       </c>
@@ -25168,7 +25176,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A392" s="3">
         <v>390</v>
       </c>
@@ -25215,7 +25223,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A393" s="4">
         <v>391</v>
       </c>
@@ -25262,7 +25270,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A394" s="3">
         <v>392</v>
       </c>
@@ -25309,7 +25317,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A395" s="4">
         <v>393</v>
       </c>
@@ -25356,7 +25364,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A396" s="3">
         <v>394</v>
       </c>
@@ -25403,7 +25411,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A397" s="4">
         <v>395</v>
       </c>
@@ -25450,7 +25458,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A398" s="3">
         <v>396</v>
       </c>
@@ -25497,7 +25505,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A399" s="4">
         <v>397</v>
       </c>
@@ -25544,7 +25552,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A400" s="3">
         <v>398</v>
       </c>
@@ -25591,7 +25599,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A401" s="4">
         <v>399</v>
       </c>
@@ -25638,7 +25646,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A402" s="3">
         <v>400</v>
       </c>
@@ -25685,7 +25693,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A403" s="4">
         <v>401</v>
       </c>
@@ -25732,7 +25740,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A404" s="3">
         <v>402</v>
       </c>
@@ -25779,7 +25787,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A405" s="4">
         <v>403</v>
       </c>
@@ -25826,7 +25834,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A406" s="3">
         <v>404</v>
       </c>
@@ -25873,7 +25881,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A407" s="4">
         <v>405</v>
       </c>
@@ -25920,7 +25928,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A408" s="3">
         <v>406</v>
       </c>
@@ -25967,7 +25975,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A409" s="4">
         <v>407</v>
       </c>
@@ -26014,7 +26022,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A410" s="3">
         <v>408</v>
       </c>
@@ -26061,7 +26069,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A411" s="4">
         <v>409</v>
       </c>
@@ -26108,7 +26116,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A412" s="3">
         <v>410</v>
       </c>
@@ -26155,7 +26163,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A413" s="4">
         <v>411</v>
       </c>
@@ -26202,7 +26210,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A414" s="3">
         <v>412</v>
       </c>
@@ -26249,7 +26257,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A415" s="4">
         <v>413</v>
       </c>
@@ -26296,7 +26304,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A416" s="3">
         <v>414</v>
       </c>
@@ -26343,7 +26351,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A417" s="4">
         <v>415</v>
       </c>
@@ -26390,7 +26398,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A418" s="3">
         <v>416</v>
       </c>
@@ -26437,7 +26445,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A419" s="4">
         <v>417</v>
       </c>
@@ -26484,7 +26492,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A420" s="3">
         <v>418</v>
       </c>
@@ -26531,7 +26539,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A421" s="4">
         <v>419</v>
       </c>
@@ -26578,7 +26586,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A422" s="3">
         <v>420</v>
       </c>
@@ -26625,7 +26633,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A423" s="4">
         <v>421</v>
       </c>
@@ -26672,7 +26680,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A424" s="3">
         <v>422</v>
       </c>
@@ -26719,7 +26727,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A425" s="4">
         <v>423</v>
       </c>
@@ -26766,7 +26774,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A426" s="3">
         <v>424</v>
       </c>
@@ -26813,7 +26821,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A427" s="4">
         <v>425</v>
       </c>
@@ -26860,7 +26868,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A428" s="3">
         <v>426</v>
       </c>
@@ -26907,7 +26915,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A429" s="4">
         <v>427</v>
       </c>
@@ -26954,7 +26962,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A430" s="3">
         <v>428</v>
       </c>
@@ -27001,7 +27009,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A431" s="4">
         <v>429</v>
       </c>
@@ -27048,7 +27056,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A432" s="3">
         <v>430</v>
       </c>
@@ -27095,7 +27103,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="433" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A433" s="4">
         <v>431</v>
       </c>
@@ -27142,7 +27150,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A434" s="3">
         <v>432</v>
       </c>
@@ -27189,7 +27197,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="435" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A435" s="4">
         <v>433</v>
       </c>
@@ -27236,7 +27244,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A436" s="3">
         <v>434</v>
       </c>
@@ -27283,7 +27291,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="437" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A437" s="4">
         <v>435</v>
       </c>
@@ -27330,7 +27338,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A438" s="3">
         <v>436</v>
       </c>
@@ -27377,7 +27385,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="439" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A439" s="4">
         <v>437</v>
       </c>
@@ -27424,7 +27432,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="440" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A440" s="3">
         <v>438</v>
       </c>
@@ -27471,7 +27479,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="441" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A441" s="4">
         <v>439</v>
       </c>
@@ -27518,7 +27526,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="442" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A442" s="3">
         <v>440</v>
       </c>
@@ -27565,7 +27573,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="443" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A443" s="4">
         <v>441</v>
       </c>
@@ -27612,7 +27620,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="444" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A444" s="3">
         <v>442</v>
       </c>
@@ -27659,7 +27667,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="445" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A445" s="4">
         <v>443</v>
       </c>
@@ -27706,7 +27714,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="446" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A446" s="3">
         <v>444</v>
       </c>
@@ -27753,7 +27761,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="447" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A447" s="4">
         <v>445</v>
       </c>
@@ -27800,7 +27808,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="448" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A448" s="3">
         <v>446</v>
       </c>
@@ -27847,7 +27855,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A449" s="4">
         <v>447</v>
       </c>
@@ -27894,7 +27902,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A450" s="3">
         <v>448</v>
       </c>
@@ -27941,7 +27949,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A451" s="4">
         <v>449</v>
       </c>
@@ -27988,7 +27996,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A452" s="3">
         <v>450</v>
       </c>
@@ -28035,7 +28043,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A453" s="4">
         <v>451</v>
       </c>
@@ -28082,7 +28090,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A454" s="3">
         <v>452</v>
       </c>
@@ -28129,7 +28137,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A455" s="4">
         <v>453</v>
       </c>
@@ -28176,7 +28184,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A456" s="3">
         <v>454</v>
       </c>
@@ -28223,7 +28231,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A457" s="4">
         <v>455</v>
       </c>
@@ -28270,7 +28278,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A458" s="3">
         <v>456</v>
       </c>
@@ -28317,7 +28325,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A459" s="4">
         <v>457</v>
       </c>
@@ -28364,7 +28372,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A460" s="3">
         <v>458</v>
       </c>
@@ -28411,7 +28419,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A461" s="4">
         <v>459</v>
       </c>
@@ -28458,7 +28466,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A462" s="3">
         <v>460</v>
       </c>
@@ -28505,7 +28513,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A463" s="4">
         <v>461</v>
       </c>
@@ -28552,7 +28560,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A464" s="3">
         <v>462</v>
       </c>
@@ -28599,7 +28607,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A465" s="4">
         <v>463</v>
       </c>
@@ -28646,7 +28654,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A466" s="3">
         <v>464</v>
       </c>
@@ -28693,7 +28701,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A467" s="4">
         <v>465</v>
       </c>
@@ -28740,7 +28748,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A468" s="3">
         <v>466</v>
       </c>
@@ -28787,7 +28795,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A469" s="4">
         <v>467</v>
       </c>
@@ -28834,7 +28842,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A470" s="3">
         <v>468</v>
       </c>
@@ -28881,7 +28889,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A471" s="4">
         <v>469</v>
       </c>
@@ -28928,7 +28936,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A472" s="3">
         <v>470</v>
       </c>
@@ -28975,7 +28983,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A473" s="4">
         <v>471</v>
       </c>
@@ -29022,7 +29030,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A474" s="3">
         <v>472</v>
       </c>
@@ -29069,7 +29077,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A475" s="4">
         <v>473</v>
       </c>
@@ -29116,7 +29124,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A476" s="3">
         <v>474</v>
       </c>
@@ -29163,7 +29171,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A477" s="4">
         <v>475</v>
       </c>
@@ -29210,7 +29218,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A478" s="3">
         <v>476</v>
       </c>
@@ -29257,7 +29265,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A479" s="4">
         <v>477</v>
       </c>
@@ -29304,7 +29312,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A480" s="3">
         <v>478</v>
       </c>
@@ -29351,7 +29359,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A481" s="4">
         <v>479</v>
       </c>
@@ -29398,7 +29406,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A482" s="3">
         <v>480</v>
       </c>
@@ -29445,7 +29453,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A483" s="4">
         <v>481</v>
       </c>
@@ -29492,7 +29500,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A484" s="3">
         <v>482</v>
       </c>
@@ -29539,7 +29547,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A485" s="4">
         <v>483</v>
       </c>
@@ -29586,7 +29594,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A486" s="3">
         <v>484</v>
       </c>
@@ -29633,7 +29641,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A487" s="4">
         <v>485</v>
       </c>
@@ -29680,7 +29688,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A488" s="3">
         <v>486</v>
       </c>
@@ -29727,7 +29735,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="489" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A489" s="4">
         <v>487</v>
       </c>
@@ -29774,7 +29782,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A490" s="3">
         <v>488</v>
       </c>
@@ -29821,7 +29829,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="491" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A491" s="4">
         <v>489</v>
       </c>
@@ -29868,7 +29876,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A492" s="3">
         <v>490</v>
       </c>
@@ -29915,7 +29923,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A493" s="4">
         <v>491</v>
       </c>
@@ -29962,7 +29970,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A494" s="3">
         <v>492</v>
       </c>
@@ -30009,7 +30017,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A495" s="4">
         <v>493</v>
       </c>
@@ -30056,7 +30064,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="496" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A496" s="3">
         <v>494</v>
       </c>
@@ -30103,7 +30111,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="497" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A497" s="4">
         <v>495</v>
       </c>
@@ -30150,7 +30158,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="498" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A498" s="3">
         <v>496</v>
       </c>
@@ -30197,7 +30205,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="499" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A499" s="4">
         <v>497</v>
       </c>
@@ -30244,7 +30252,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="500" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A500" s="3">
         <v>498</v>
       </c>
@@ -30291,7 +30299,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="501" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A501" s="4">
         <v>499</v>
       </c>
@@ -30338,7 +30346,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="502" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A502" s="3">
         <v>500</v>
       </c>
@@ -30385,7 +30393,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="503" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A503" s="4">
         <v>501</v>
       </c>
@@ -30432,7 +30440,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="504" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A504" s="3">
         <v>502</v>
       </c>
@@ -30479,7 +30487,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="505" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A505" s="4">
         <v>503</v>
       </c>
@@ -30526,7 +30534,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="506" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A506" s="3">
         <v>504</v>
       </c>
@@ -30573,7 +30581,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="507" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A507" s="4">
         <v>505</v>
       </c>
@@ -30620,7 +30628,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="508" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A508" s="3">
         <v>506</v>
       </c>
@@ -30669,14 +30677,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -30687,18 +30695,18 @@
     <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>476</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="2" spans="1:7" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>477</v>
       </c>
@@ -30721,7 +30729,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>415</v>
       </c>
@@ -30744,7 +30752,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>417</v>
       </c>
@@ -30767,7 +30775,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>419</v>
       </c>
@@ -30790,7 +30798,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>421</v>
       </c>
@@ -30813,7 +30821,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>423</v>
       </c>
@@ -30836,7 +30844,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>425</v>
       </c>
@@ -30859,7 +30867,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>427</v>
       </c>
@@ -30882,7 +30890,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>429</v>
       </c>
@@ -30905,7 +30913,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>431</v>
       </c>
@@ -30928,7 +30936,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>442</v>
       </c>
@@ -30951,7 +30959,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>445</v>
       </c>
@@ -30974,7 +30982,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>507</v>
       </c>
@@ -30997,7 +31005,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>510</v>
       </c>
@@ -31020,7 +31028,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>513</v>
       </c>
@@ -31043,7 +31051,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>516</v>
       </c>
@@ -31066,7 +31074,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>390</v>
       </c>
@@ -31089,7 +31097,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>392</v>
       </c>
@@ -31112,7 +31120,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>394</v>
       </c>
@@ -31135,7 +31143,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>396</v>
       </c>
@@ -31158,7 +31166,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>399</v>
       </c>
@@ -31181,7 +31189,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>401</v>
       </c>
@@ -31204,7 +31212,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>404</v>
       </c>
@@ -31227,7 +31235,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>407</v>
       </c>
@@ -31250,7 +31258,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>409</v>
       </c>
@@ -31273,7 +31281,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>412</v>
       </c>
@@ -31296,7 +31304,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>528</v>
       </c>
@@ -31319,7 +31327,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>530</v>
       </c>
@@ -31342,7 +31350,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>532</v>
       </c>
@@ -31365,7 +31373,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>534</v>
       </c>
@@ -31388,7 +31396,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>536</v>
       </c>
@@ -31411,7 +31419,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>537</v>
       </c>
@@ -31434,7 +31442,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>540</v>
       </c>
@@ -31457,7 +31465,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>543</v>
       </c>
@@ -31480,7 +31488,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>546</v>
       </c>
@@ -31503,7 +31511,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>549</v>
       </c>
@@ -31526,7 +31534,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>550</v>
       </c>
@@ -31549,7 +31557,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>552</v>
       </c>
@@ -31572,7 +31580,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>553</v>
       </c>
@@ -31595,7 +31603,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>554</v>
       </c>
@@ -31618,7 +31626,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>555</v>
       </c>
@@ -31641,7 +31649,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>556</v>
       </c>
@@ -31664,7 +31672,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>557</v>
       </c>
@@ -31687,7 +31695,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>558</v>
       </c>
@@ -31710,7 +31718,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>559</v>
       </c>
@@ -31733,7 +31741,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>562</v>
       </c>
@@ -31756,7 +31764,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>564</v>
       </c>
@@ -31779,7 +31787,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
         <v>567</v>
       </c>
@@ -31807,14 +31815,14 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:N73"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -31827,7 +31835,7 @@
     <col min="14" max="14" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>569</v>
       </c>
@@ -31871,7 +31879,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="2" ht="27.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>93</v>
       </c>
@@ -31915,7 +31923,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>103</v>
       </c>
@@ -31955,7 +31963,7 @@
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>109</v>
       </c>
@@ -31995,7 +32003,7 @@
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>113</v>
       </c>
@@ -32035,7 +32043,7 @@
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>117</v>
       </c>
@@ -32075,7 +32083,7 @@
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>121</v>
       </c>
@@ -32115,7 +32123,7 @@
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>125</v>
       </c>
@@ -32155,7 +32163,7 @@
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>129</v>
       </c>
@@ -32195,7 +32203,7 @@
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>133</v>
       </c>
@@ -32235,7 +32243,7 @@
       <c r="M10" s="11"/>
       <c r="N10" s="11"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>137</v>
       </c>
@@ -32275,7 +32283,7 @@
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>141</v>
       </c>
@@ -32315,7 +32323,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>146</v>
       </c>
@@ -32355,7 +32363,7 @@
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>151</v>
       </c>
@@ -32395,7 +32403,7 @@
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>155</v>
       </c>
@@ -32435,7 +32443,7 @@
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>159</v>
       </c>
@@ -32475,7 +32483,7 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>163</v>
       </c>
@@ -32515,7 +32523,7 @@
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>167</v>
       </c>
@@ -32555,7 +32563,7 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>171</v>
       </c>
@@ -32595,7 +32603,7 @@
       <c r="M19" s="10"/>
       <c r="N19" s="10"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>175</v>
       </c>
@@ -32635,7 +32643,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>180</v>
       </c>
@@ -32675,7 +32683,7 @@
       <c r="M21" s="10"/>
       <c r="N21" s="10"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>185</v>
       </c>
@@ -32715,7 +32723,7 @@
       <c r="M22" s="11"/>
       <c r="N22" s="11"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>189</v>
       </c>
@@ -32755,7 +32763,7 @@
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>193</v>
       </c>
@@ -32795,7 +32803,7 @@
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>197</v>
       </c>
@@ -32835,7 +32843,7 @@
       <c r="M25" s="10"/>
       <c r="N25" s="10"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>201</v>
       </c>
@@ -32875,7 +32883,7 @@
       <c r="M26" s="11"/>
       <c r="N26" s="11"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>205</v>
       </c>
@@ -32915,7 +32923,7 @@
       <c r="M27" s="10"/>
       <c r="N27" s="10"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>209</v>
       </c>
@@ -32955,7 +32963,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>214</v>
       </c>
@@ -32995,7 +33003,7 @@
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>219</v>
       </c>
@@ -33035,7 +33043,7 @@
       <c r="M30" s="11"/>
       <c r="N30" s="11"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>223</v>
       </c>
@@ -33075,7 +33083,7 @@
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>227</v>
       </c>
@@ -33115,7 +33123,7 @@
       <c r="M32" s="11"/>
       <c r="N32" s="11"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>231</v>
       </c>
@@ -33155,7 +33163,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>236</v>
       </c>
@@ -33195,7 +33203,7 @@
       <c r="M34" s="11"/>
       <c r="N34" s="11"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>241</v>
       </c>
@@ -33235,7 +33243,7 @@
       <c r="M35" s="10"/>
       <c r="N35" s="10"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>245</v>
       </c>
@@ -33275,7 +33283,7 @@
       <c r="M36" s="11"/>
       <c r="N36" s="11"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>249</v>
       </c>
@@ -33315,7 +33323,7 @@
       <c r="M37" s="10"/>
       <c r="N37" s="10"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>253</v>
       </c>
@@ -33355,7 +33363,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>258</v>
       </c>
@@ -33395,7 +33403,7 @@
       <c r="M39" s="10"/>
       <c r="N39" s="10"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>262</v>
       </c>
@@ -33435,7 +33443,7 @@
       <c r="M40" s="11"/>
       <c r="N40" s="11"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>266</v>
       </c>
@@ -33475,7 +33483,7 @@
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>270</v>
       </c>
@@ -33515,7 +33523,7 @@
       <c r="M42" s="11"/>
       <c r="N42" s="11"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>274</v>
       </c>
@@ -33555,7 +33563,7 @@
       <c r="M43" s="10"/>
       <c r="N43" s="10"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>277</v>
       </c>
@@ -33595,7 +33603,7 @@
       <c r="M44" s="11"/>
       <c r="N44" s="11"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>281</v>
       </c>
@@ -33635,7 +33643,7 @@
       <c r="M45" s="10"/>
       <c r="N45" s="10"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>284</v>
       </c>
@@ -33675,7 +33683,7 @@
       <c r="M46" s="11"/>
       <c r="N46" s="11"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>287</v>
       </c>
@@ -33715,7 +33723,7 @@
       <c r="M47" s="10"/>
       <c r="N47" s="10"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>292</v>
       </c>
@@ -33755,7 +33763,7 @@
       <c r="M48" s="11"/>
       <c r="N48" s="11"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>296</v>
       </c>
@@ -33795,7 +33803,7 @@
       <c r="M49" s="10"/>
       <c r="N49" s="10"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>300</v>
       </c>
@@ -33835,7 +33843,7 @@
       <c r="M50" s="11"/>
       <c r="N50" s="11"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>304</v>
       </c>
@@ -33875,7 +33883,7 @@
       <c r="M51" s="10"/>
       <c r="N51" s="10"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>307</v>
       </c>
@@ -33915,7 +33923,7 @@
       <c r="M52" s="11"/>
       <c r="N52" s="11"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>311</v>
       </c>
@@ -33955,7 +33963,7 @@
       <c r="M53" s="10"/>
       <c r="N53" s="10"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>314</v>
       </c>
@@ -33995,7 +34003,7 @@
       <c r="M54" s="11"/>
       <c r="N54" s="11"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>317</v>
       </c>
@@ -34035,7 +34043,7 @@
       <c r="M55" s="10"/>
       <c r="N55" s="10"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>320</v>
       </c>
@@ -34075,7 +34083,7 @@
       <c r="M56" s="11"/>
       <c r="N56" s="11"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>324</v>
       </c>
@@ -34115,7 +34123,7 @@
       <c r="M57" s="10"/>
       <c r="N57" s="10"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>327</v>
       </c>
@@ -34155,7 +34163,7 @@
       <c r="M58" s="11"/>
       <c r="N58" s="11"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>330</v>
       </c>
@@ -34195,7 +34203,7 @@
       <c r="M59" s="10"/>
       <c r="N59" s="10"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>334</v>
       </c>
@@ -34235,7 +34243,7 @@
       <c r="M60" s="10"/>
       <c r="N60" s="10"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>338</v>
       </c>
@@ -34275,7 +34283,7 @@
       <c r="M61" s="11"/>
       <c r="N61" s="11"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>341</v>
       </c>
@@ -34315,7 +34323,7 @@
       <c r="M62" s="10"/>
       <c r="N62" s="10"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>344</v>
       </c>
@@ -34355,7 +34363,7 @@
       <c r="M63" s="11"/>
       <c r="N63" s="11"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>347</v>
       </c>
@@ -34395,7 +34403,7 @@
       <c r="M64" s="10"/>
       <c r="N64" s="10"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>350</v>
       </c>
@@ -34435,7 +34443,7 @@
       <c r="M65" s="11"/>
       <c r="N65" s="11"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>354</v>
       </c>
@@ -34475,7 +34483,7 @@
       <c r="M66" s="10"/>
       <c r="N66" s="10"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>357</v>
       </c>
@@ -34515,7 +34523,7 @@
       <c r="M67" s="11"/>
       <c r="N67" s="11"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>360</v>
       </c>
@@ -34555,7 +34563,7 @@
       <c r="M68" s="10"/>
       <c r="N68" s="10"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>364</v>
       </c>
@@ -34595,7 +34603,7 @@
       <c r="M69" s="11"/>
       <c r="N69" s="11"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>367</v>
       </c>
@@ -34635,7 +34643,7 @@
       <c r="M70" s="10"/>
       <c r="N70" s="10"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>370</v>
       </c>
@@ -34675,7 +34683,7 @@
       <c r="M71" s="11"/>
       <c r="N71" s="11"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>373</v>
       </c>
@@ -34715,7 +34723,7 @@
       <c r="M72" s="10"/>
       <c r="N72" s="10"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>376</v>
       </c>
@@ -34757,6 +34765,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>